--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_397_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_397_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
         <v>6</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>15</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1341,10 +1341,10 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>2</v>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>57:34</t>
+          <t>32:34</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
     </row>
@@ -1531,10 +1531,10 @@
         <v>29</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>84:17</t>
+          <t>39:17</t>
         </is>
       </c>
       <c r="AN18" t="n">
@@ -1647,22 +1647,22 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>65.4%</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>2</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>69:29</t>
+          <t>29:29</t>
         </is>
       </c>
       <c r="AN19" t="n">
@@ -1843,22 +1843,22 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>7.5%</t>
         </is>
       </c>
     </row>
@@ -2315,10 +2315,10 @@
         <v>17</v>
       </c>
       <c r="T22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>71:21</t>
+          <t>36:21</t>
         </is>
       </c>
       <c r="AN22" t="n">
@@ -2431,17 +2431,17 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AN23" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>19.9%</t>
         </is>
       </c>
     </row>
@@ -2713,10 +2713,10 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>3</v>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>36:49</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="AN24" t="n">
@@ -2823,17 +2823,17 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>40:02</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AN26" t="n">
@@ -3215,22 +3215,22 @@
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>9.0%</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3494,13 +3494,13 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>5</v>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>58:24</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AN28" t="n">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -3827,16 +3827,16 @@
         <v>96</v>
       </c>
       <c r="T30" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="W30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
         <v>37</v>
@@ -4295,13 +4295,13 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
         <v>3</v>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>71:15</t>
+          <t>36:14</t>
         </is>
       </c>
       <c r="AN35" t="n">
@@ -4408,22 +4408,22 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>23.4%</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
         <v>15</v>
       </c>
       <c r="T36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>78:32</t>
+          <t>33:32</t>
         </is>
       </c>
       <c r="AN36" t="n">
@@ -4604,17 +4604,17 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
@@ -4684,16 +4684,16 @@
         <v>24</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>12</v>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>41:08</t>
+          <t>26:09</t>
         </is>
       </c>
       <c r="AN37" t="n">
@@ -4800,22 +4800,22 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>25.5%</t>
         </is>
       </c>
     </row>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>00:53</t>
         </is>
       </c>
       <c r="AN38" t="n">
@@ -5082,10 +5082,10 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
         <v>3</v>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>68:24</t>
+          <t>28:24</t>
         </is>
       </c>
       <c r="AN40" t="n">
@@ -5388,22 +5388,22 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
+          <t>17.4%</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
           <t>7.2%</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>3.0%</t>
-        </is>
-      </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>11.5%</t>
         </is>
       </c>
     </row>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>44:09</t>
+          <t>29:09</t>
         </is>
       </c>
       <c r="AN43" t="n">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
@@ -5986,12 +5986,12 @@
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>15.0%</t>
         </is>
       </c>
     </row>
@@ -6258,10 +6258,10 @@
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>1</v>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>28:25</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AN45" t="n">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
@@ -6451,13 +6451,13 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
         <v>12</v>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>78:53</t>
+          <t>33:53</t>
         </is>
       </c>
       <c r="AN46" t="n">
@@ -6564,17 +6564,17 @@
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
@@ -6784,16 +6784,16 @@
         <v>112</v>
       </c>
       <c r="T48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
         <v>40</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_397_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_397_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M2" t="n">
         <v>6</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M3" t="n">
         <v>15</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1341,10 +1341,10 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
         <v>2</v>
@@ -1531,10 +1531,10 @@
         <v>29</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V19" t="n">
         <v>2</v>
@@ -2315,10 +2315,10 @@
         <v>17</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2713,10 +2713,10 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X24" t="n">
         <v>3</v>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3494,13 +3494,13 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X28" t="n">
         <v>5</v>
@@ -3827,16 +3827,16 @@
         <v>96</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="V30" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X30" t="n">
         <v>37</v>
@@ -4295,13 +4295,13 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
         <v>3</v>
@@ -4488,7 +4488,7 @@
         <v>15</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -4684,16 +4684,16 @@
         <v>24</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X37" t="n">
         <v>12</v>
@@ -5082,10 +5082,10 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X39" t="n">
         <v>3</v>
@@ -6258,10 +6258,10 @@
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X45" t="n">
         <v>1</v>
@@ -6451,13 +6451,13 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X46" t="n">
         <v>12</v>
@@ -6784,16 +6784,16 @@
         <v>112</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X48" t="n">
         <v>40</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_397_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_397_EL.xlsx
@@ -674,10 +674,10 @@
         <v>6</v>
       </c>
       <c r="N2" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="O2" t="n">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
@@ -692,20 +692,20 @@
         <v>9</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>78.72</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>36.67</t>
+          <t>34.48</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>15</v>
       </c>
       <c r="N3" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="O3" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="P3" t="n">
         <v>5</v>
@@ -854,17 +854,17 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
         <v>6</v>
       </c>
       <c r="W3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>80.77</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,14 +1347,14 @@
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -1543,14 +1543,14 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA18" t="n">
@@ -1739,14 +1739,14 @@
         <v>1</v>
       </c>
       <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
         <v>4</v>
       </c>
-      <c r="Y19" t="n">
-        <v>7</v>
-      </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -2327,14 +2327,14 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Y22" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA22" t="n">
@@ -2719,14 +2719,14 @@
         <v>1</v>
       </c>
       <c r="X24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA24" t="n">
@@ -2752,25 +2752,25 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AJ24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK24" t="n">
         <v>2</v>
       </c>
-      <c r="AK24" t="n">
-        <v>3</v>
-      </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
@@ -3111,14 +3111,14 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA26" t="n">
@@ -3503,10 +3503,10 @@
         <v>2</v>
       </c>
       <c r="X28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -3839,14 +3839,14 @@
         <v>5</v>
       </c>
       <c r="X30" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="Y30" t="n">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -3872,25 +3872,25 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4304,10 +4304,10 @@
         <v>1</v>
       </c>
       <c r="X35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
@@ -4500,10 +4500,10 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -4696,14 +4696,14 @@
         <v>4</v>
       </c>
       <c r="X37" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Y37" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -5088,14 +5088,14 @@
         <v>2</v>
       </c>
       <c r="X39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA39" t="n">
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
@@ -5919,11 +5919,11 @@
         <v>1</v>
       </c>
       <c r="AK43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
@@ -6068,10 +6068,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
@@ -6264,14 +6264,14 @@
         <v>1</v>
       </c>
       <c r="X45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA45" t="n">
@@ -6460,14 +6460,14 @@
         <v>2</v>
       </c>
       <c r="X46" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Y46" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="AA46" t="n">
@@ -6796,14 +6796,14 @@
         <v>10</v>
       </c>
       <c r="X48" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="Y48" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="AA48" t="n">
@@ -6832,22 +6832,22 @@
         <v>1</v>
       </c>
       <c r="AH48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AJ48" t="n">
         <v>6</v>
       </c>
       <c r="AK48" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
